--- a/document/cv.xlsx
+++ b/document/cv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\履歴書\株式会社トマート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\my-website\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A4DA23-4F04-4200-8401-05528CC63041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CCB0B81-E3F5-447C-8836-8797032F1A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0322D4C2-D3BE-4B46-AFF3-B59D68C0BA36}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{0322D4C2-D3BE-4B46-AFF3-B59D68C0BA36}"/>
   </bookViews>
   <sheets>
     <sheet name="入力用 (フォント大‗空)" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">印刷用見本!$A$1:$L$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'入力用 (フォント大‗空)'!$A$1:$L$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'入力用 (フォント大‗空)'!$A$1:$L$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
   <si>
     <t>フリガナ</t>
     <phoneticPr fontId="2"/>
@@ -959,20 +959,26 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Javaプログラミング能力認定試験　3級結果持ち</t>
+  </si>
+  <si>
+    <t>情報処理技術者能力認定試験　3級結果持ち</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy&quot; 年&quot;\ m&quot; 月&quot;\ d&quot; 日&quot;"/>
-    <numFmt numFmtId="177" formatCode="yyyy&quot; 年&quot;\ m&quot; 月&quot;\ d&quot; 日 現在&quot;"/>
+    <numFmt numFmtId="164" formatCode="yyyy&quot; 年&quot;\ m&quot; 月&quot;\ d&quot; 日&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot; 年&quot;\ m&quot; 月&quot;\ d&quot; 日 現在&quot;"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -986,7 +992,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1001,7 +1007,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1009,7 +1015,7 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1017,7 +1023,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1025,7 +1031,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1033,7 +1039,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1041,7 +1047,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1050,7 +1056,7 @@
       <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1058,7 +1064,7 @@
     <font>
       <b/>
       <sz val="18"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1786,25 +1792,208 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1812,16 +2001,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1843,209 +2022,258 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2074,231 +2302,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2431,7 +2437,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>512447</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>126370</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1380395" cy="370350"/>
@@ -2777,7 +2783,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -3073,81 +3079,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B1A889-D6F8-4F4E-96C9-B236DCF218AB}">
-  <dimension ref="A1:L59"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" customWidth="1"/>
-    <col min="2" max="2" width="7.09765625" customWidth="1"/>
-    <col min="3" max="3" width="5.69921875" customWidth="1"/>
-    <col min="4" max="4" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="3.3984375" customWidth="1"/>
-    <col min="7" max="7" width="5.59765625" customWidth="1"/>
-    <col min="8" max="8" width="3.59765625" customWidth="1"/>
+    <col min="6" max="6" width="3.44140625" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" customWidth="1"/>
+    <col min="8" max="8" width="3.5546875" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="8.3984375" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
+      <c r="A1" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="119"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="51">
+      <c r="E1" s="122">
         <f ca="1">TODAY()</f>
-        <v>46225</v>
-      </c>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
+        <v>46236</v>
+      </c>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+    </row>
+    <row r="2" spans="1:12" ht="18.75" customHeight="1">
+      <c r="A2" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="49" t="s">
+      <c r="B2" s="106"/>
+      <c r="C2" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-    </row>
-    <row r="3" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="121"/>
+    </row>
+    <row r="3" spans="1:12" ht="48" customHeight="1">
+      <c r="A3" s="113" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42" t="s">
+      <c r="B3" s="114"/>
+      <c r="C3" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="4" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="40" t="s">
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="117"/>
+    </row>
+    <row r="4" spans="1:12" ht="24" customHeight="1">
+      <c r="A4" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="45">
+      <c r="B4" s="114"/>
+      <c r="C4" s="118">
         <v>36909</v>
       </c>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
       <c r="F4" s="28" t="s">
         <v>18</v>
       </c>
@@ -3165,529 +3171,529 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="54" t="s">
+    <row r="5" spans="1:12" ht="24" customHeight="1">
+      <c r="A5" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56" t="s">
+      <c r="B5" s="110"/>
+      <c r="C5" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56" t="s">
+      <c r="D5" s="111"/>
+      <c r="E5" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56" t="s">
+      <c r="F5" s="111"/>
+      <c r="G5" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
-    </row>
-    <row r="6" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="47" t="s">
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="112"/>
+    </row>
+    <row r="6" spans="1:12" ht="6" customHeight="1"/>
+    <row r="7" spans="1:12" ht="18.75" customHeight="1">
+      <c r="A7" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="52" t="s">
+      <c r="B7" s="106"/>
+      <c r="C7" s="107" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="53"/>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="63" t="s">
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="108"/>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" customHeight="1">
+      <c r="A8" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="71" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="68"/>
-    </row>
-    <row r="9" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="65"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="69" t="s">
+      <c r="D8" s="95"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="91"/>
+    </row>
+    <row r="9" spans="1:12" ht="48" customHeight="1">
+      <c r="A9" s="88"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="92" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="70"/>
-    </row>
-    <row r="10" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="80" t="s">
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="93"/>
+    </row>
+    <row r="10" spans="1:12" ht="24" customHeight="1">
+      <c r="A10" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="82" t="s">
+      <c r="B10" s="102"/>
+      <c r="C10" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="83" t="s">
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="59"/>
-      <c r="J10" s="58" t="s">
+      <c r="I10" s="82"/>
+      <c r="J10" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="59"/>
-      <c r="L10" s="60"/>
-    </row>
-    <row r="11" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="73" t="s">
+      <c r="K10" s="82"/>
+      <c r="L10" s="83"/>
+    </row>
+    <row r="11" spans="1:12" ht="24" customHeight="1">
+      <c r="A11" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75" t="s">
+      <c r="B11" s="49"/>
+      <c r="C11" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
-    </row>
-    <row r="12" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="99"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" spans="1:12" ht="6" customHeight="1"/>
+    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="86"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="86"/>
-      <c r="I13" s="86"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="87"/>
-    </row>
-    <row r="14" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
+    </row>
+    <row r="14" spans="1:12" ht="23.1" customHeight="1">
       <c r="A14" s="32"/>
       <c r="B14" s="33"/>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="88"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="89"/>
-    </row>
-    <row r="15" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="80"/>
+    </row>
+    <row r="15" spans="1:12" ht="22.2" customHeight="1">
       <c r="A15" s="24">
         <v>2017</v>
       </c>
       <c r="B15" s="25">
         <v>6</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="85"/>
-    </row>
-    <row r="16" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
+    </row>
+    <row r="16" spans="1:12" ht="22.2" customHeight="1">
       <c r="A16" s="24">
         <v>2019</v>
       </c>
       <c r="B16" s="25">
         <v>8</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="84"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84"/>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="85"/>
-    </row>
-    <row r="17" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="63"/>
+    </row>
+    <row r="17" spans="1:12" ht="22.2" customHeight="1">
       <c r="A17" s="24">
         <v>2021</v>
       </c>
       <c r="B17" s="25">
         <v>1</v>
       </c>
-      <c r="C17" s="84" t="s">
+      <c r="C17" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="85"/>
-    </row>
-    <row r="18" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
+      <c r="J17" s="62"/>
+      <c r="K17" s="62"/>
+      <c r="L17" s="63"/>
+    </row>
+    <row r="18" spans="1:12" ht="22.2" customHeight="1">
       <c r="A18" s="24">
         <v>2021</v>
       </c>
       <c r="B18" s="25">
         <v>8</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="84"/>
-      <c r="E18" s="84"/>
-      <c r="F18" s="84"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="84"/>
-      <c r="I18" s="84"/>
-      <c r="J18" s="84"/>
-      <c r="K18" s="84"/>
-      <c r="L18" s="85"/>
-    </row>
-    <row r="19" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="63"/>
+    </row>
+    <row r="19" spans="1:12" ht="22.2" customHeight="1">
       <c r="A19" s="24">
         <v>2023</v>
       </c>
       <c r="B19" s="25">
         <v>7</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
-      <c r="J19" s="84"/>
-      <c r="K19" s="84"/>
-      <c r="L19" s="85"/>
-    </row>
-    <row r="20" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="63"/>
+    </row>
+    <row r="20" spans="1:12" ht="22.2" customHeight="1">
       <c r="A20" s="24">
         <v>2025</v>
       </c>
       <c r="B20" s="25">
         <v>3</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="85"/>
-    </row>
-    <row r="21" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="63"/>
+    </row>
+    <row r="21" spans="1:12" ht="22.2" customHeight="1">
       <c r="A21" s="24">
         <v>2025</v>
       </c>
       <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="84"/>
-      <c r="E21" s="84"/>
-      <c r="F21" s="84"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="84"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="85"/>
-    </row>
-    <row r="22" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="63"/>
+    </row>
+    <row r="22" spans="1:12" ht="22.2" customHeight="1">
       <c r="A22" s="24">
         <v>2027</v>
       </c>
       <c r="B22" s="25">
         <v>3</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="85"/>
-    </row>
-    <row r="23" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="63"/>
+    </row>
+    <row r="23" spans="1:12" ht="22.2" customHeight="1">
       <c r="A23" s="24"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="84"/>
-      <c r="D23" s="84"/>
-      <c r="E23" s="84"/>
-      <c r="F23" s="84"/>
-      <c r="G23" s="84"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="84"/>
-      <c r="K23" s="84"/>
-      <c r="L23" s="85"/>
-    </row>
-    <row r="24" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="63"/>
+    </row>
+    <row r="24" spans="1:12" ht="22.2" customHeight="1">
       <c r="A24" s="24"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="84" t="s">
+      <c r="C24" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="85"/>
-    </row>
-    <row r="25" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D24" s="62"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="63"/>
+    </row>
+    <row r="25" spans="1:12" ht="22.2" customHeight="1">
       <c r="A25" s="24">
         <v>2019</v>
       </c>
       <c r="B25" s="25">
         <v>10</v>
       </c>
-      <c r="C25" s="84" t="s">
+      <c r="C25" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="84"/>
-      <c r="E25" s="84"/>
-      <c r="F25" s="84"/>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="84"/>
-      <c r="J25" s="84"/>
-      <c r="K25" s="84"/>
-      <c r="L25" s="85"/>
-    </row>
-    <row r="26" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="63"/>
+    </row>
+    <row r="26" spans="1:12" ht="22.2" customHeight="1">
       <c r="A26" s="24">
         <v>2023</v>
       </c>
       <c r="B26" s="25">
         <v>2</v>
       </c>
-      <c r="C26" s="84" t="s">
+      <c r="C26" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="D26" s="84"/>
-      <c r="E26" s="84"/>
-      <c r="F26" s="84"/>
-      <c r="G26" s="84"/>
-      <c r="H26" s="84"/>
-      <c r="I26" s="84"/>
-      <c r="J26" s="84"/>
-      <c r="K26" s="84"/>
-      <c r="L26" s="85"/>
-    </row>
-    <row r="27" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="63"/>
+    </row>
+    <row r="27" spans="1:12" ht="22.2" customHeight="1">
       <c r="A27" s="24"/>
       <c r="B27" s="25"/>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="91"/>
-    </row>
-    <row r="28" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="76"/>
+    </row>
+    <row r="28" spans="1:12" ht="22.2" customHeight="1">
       <c r="A28" s="24"/>
       <c r="B28" s="25"/>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="D28" s="84"/>
-      <c r="E28" s="84"/>
-      <c r="F28" s="84"/>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="84"/>
-      <c r="K28" s="84"/>
-      <c r="L28" s="85"/>
-    </row>
-    <row r="29" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="63"/>
+    </row>
+    <row r="29" spans="1:12" ht="22.2" customHeight="1">
       <c r="A29" s="24">
         <v>2023</v>
       </c>
       <c r="B29" s="25">
         <v>8</v>
       </c>
-      <c r="C29" s="84" t="s">
+      <c r="C29" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84"/>
-      <c r="G29" s="84"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="L29" s="85"/>
-    </row>
-    <row r="30" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="63"/>
+    </row>
+    <row r="30" spans="1:12" ht="22.2" customHeight="1">
       <c r="A30" s="24">
         <v>2024</v>
       </c>
       <c r="B30" s="25">
         <v>2</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="84"/>
-      <c r="E30" s="84"/>
-      <c r="F30" s="84"/>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="84"/>
-      <c r="K30" s="84"/>
-      <c r="L30" s="85"/>
-    </row>
-    <row r="31" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="63"/>
+    </row>
+    <row r="31" spans="1:12" ht="22.2" customHeight="1">
       <c r="A31" s="24">
         <v>2025</v>
       </c>
       <c r="B31" s="25">
         <v>4</v>
       </c>
-      <c r="C31" s="84" t="s">
+      <c r="C31" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
-      <c r="F31" s="84"/>
-      <c r="G31" s="84"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
-      <c r="L31" s="85"/>
-    </row>
-    <row r="32" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="63"/>
+    </row>
+    <row r="32" spans="1:12" ht="22.2" customHeight="1">
       <c r="A32" s="24">
         <v>2026</v>
       </c>
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="84" t="s">
+      <c r="C32" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="84"/>
-      <c r="K32" s="84"/>
-      <c r="L32" s="85"/>
-    </row>
-    <row r="33" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="63"/>
+    </row>
+    <row r="33" spans="1:12" ht="22.2" customHeight="1">
       <c r="A33" s="26"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="99" t="s">
+      <c r="C33" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="100"/>
-    </row>
-    <row r="34" spans="1:12" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="74"/>
+    </row>
+    <row r="34" spans="1:12" ht="22.2" customHeight="1">
       <c r="A34" s="36"/>
       <c r="B34" s="37"/>
-      <c r="C34" s="92" t="s">
+      <c r="C34" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="92"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="92"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="93"/>
-    </row>
-    <row r="35" spans="1:12" ht="3" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D34" s="66"/>
+      <c r="E34" s="66"/>
+      <c r="F34" s="66"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="66"/>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="67"/>
+    </row>
+    <row r="35" spans="1:12" ht="3" customHeight="1">
       <c r="A35" s="20"/>
       <c r="B35" s="20"/>
       <c r="C35" s="21"/>
@@ -3701,7 +3707,7 @@
       <c r="K35" s="21"/>
       <c r="L35" s="21"/>
     </row>
-    <row r="36" spans="1:12" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:12" ht="8.1" customHeight="1">
       <c r="A36" s="20"/>
       <c r="B36" s="20"/>
       <c r="C36" s="21"/>
@@ -3715,413 +3721,422 @@
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
     </row>
-    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="22" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="94" t="s">
+      <c r="C37" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="94"/>
-      <c r="J37" s="94"/>
-      <c r="K37" s="94"/>
-      <c r="L37" s="95"/>
-    </row>
-    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D37" s="68"/>
+      <c r="E37" s="68"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="68"/>
+      <c r="J37" s="68"/>
+      <c r="K37" s="68"/>
+      <c r="L37" s="69"/>
+    </row>
+    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A38" s="34">
         <v>2021</v>
       </c>
       <c r="B38" s="35">
         <v>8</v>
       </c>
-      <c r="C38" s="96" t="s">
+      <c r="C38" s="70" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="97"/>
-      <c r="E38" s="97"/>
-      <c r="F38" s="97"/>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="98"/>
-    </row>
-    <row r="39" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="72"/>
+    </row>
+    <row r="39" spans="1:12" ht="23.1" customHeight="1">
       <c r="A39" s="24">
         <v>2025</v>
       </c>
       <c r="B39" s="25">
         <v>12</v>
       </c>
-      <c r="C39" s="84" t="s">
+      <c r="C39" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="84"/>
-      <c r="L39" s="85"/>
-    </row>
-    <row r="40" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
+      <c r="J39" s="62"/>
+      <c r="K39" s="62"/>
+      <c r="L39" s="63"/>
+    </row>
+    <row r="40" spans="1:12" ht="23.1" customHeight="1">
       <c r="A40" s="24">
         <v>2026</v>
       </c>
       <c r="B40" s="25">
         <v>3</v>
       </c>
-      <c r="C40" s="107" t="s">
+      <c r="C40" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="D40" s="84"/>
-      <c r="E40" s="84"/>
-      <c r="F40" s="84"/>
-      <c r="G40" s="84"/>
-      <c r="H40" s="84"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="84"/>
-      <c r="L40" s="85"/>
-    </row>
-    <row r="41" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="62"/>
+      <c r="L40" s="63"/>
+    </row>
+    <row r="41" spans="1:12" ht="23.1" customHeight="1">
       <c r="A41" s="24">
         <v>2026</v>
       </c>
       <c r="B41" s="25">
         <v>3</v>
       </c>
-      <c r="C41" s="84" t="s">
+      <c r="C41" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="85"/>
-    </row>
-    <row r="42" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="62"/>
+      <c r="K41" s="62"/>
+      <c r="L41" s="63"/>
+    </row>
+    <row r="42" spans="1:12" ht="23.1" customHeight="1">
       <c r="A42" s="24">
         <v>2026</v>
       </c>
       <c r="B42" s="25">
         <v>7</v>
       </c>
-      <c r="C42" s="84" t="s">
+      <c r="C42" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
+      <c r="J42" s="62"/>
+      <c r="K42" s="62"/>
+      <c r="L42" s="63"/>
+    </row>
+    <row r="43" spans="1:12" ht="23.1" customHeight="1">
+      <c r="A43" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B43" s="25">
+        <v>7</v>
+      </c>
+      <c r="C43" s="62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
+      <c r="J43" s="62"/>
+      <c r="K43" s="62"/>
+      <c r="L43" s="63"/>
+    </row>
+    <row r="44" spans="1:12" ht="23.1" customHeight="1">
+      <c r="A44" s="24">
+        <v>2026</v>
+      </c>
+      <c r="B44" s="25">
+        <v>7</v>
+      </c>
+      <c r="C44" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="84"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="85"/>
-    </row>
-    <row r="43" spans="1:12" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="39"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="105"/>
-      <c r="E43" s="105"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="105"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="105"/>
-      <c r="J43" s="105"/>
-      <c r="K43" s="105"/>
-      <c r="L43" s="106"/>
-    </row>
-    <row r="44" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-    </row>
-    <row r="45" spans="1:12" ht="42.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="101" t="s">
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
+      <c r="J44" s="62"/>
+      <c r="K44" s="62"/>
+      <c r="L44" s="63"/>
+    </row>
+    <row r="45" spans="1:12" ht="23.1" customHeight="1">
+      <c r="A45" s="39"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
+      <c r="L45" s="65"/>
+    </row>
+    <row r="46" spans="1:12" ht="6" customHeight="1">
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+    </row>
+    <row r="47" spans="1:12" ht="42.9" customHeight="1">
+      <c r="A47" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B45" s="102"/>
-      <c r="C45" s="102"/>
-      <c r="D45" s="103" t="s">
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="103"/>
-      <c r="J45" s="103"/>
-      <c r="K45" s="103"/>
-      <c r="L45" s="104"/>
-    </row>
-    <row r="46" spans="1:12" ht="42.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="114" t="s">
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="61"/>
+    </row>
+    <row r="48" spans="1:12" ht="42.9" customHeight="1">
+      <c r="A48" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="B46" s="115"/>
-      <c r="C46" s="115"/>
-      <c r="D46" s="107" t="s">
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="E46" s="107"/>
-      <c r="F46" s="107"/>
-      <c r="G46" s="107"/>
-      <c r="H46" s="107"/>
-      <c r="I46" s="107"/>
-      <c r="J46" s="107"/>
-      <c r="K46" s="107"/>
-      <c r="L46" s="116"/>
-    </row>
-    <row r="47" spans="1:12" ht="42.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="117" t="s">
+      <c r="E48" s="54"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="54"/>
+      <c r="L48" s="55"/>
+    </row>
+    <row r="49" spans="1:12" ht="42.9" customHeight="1">
+      <c r="A49" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="B47" s="118"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="107" t="s">
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="107"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="107"/>
-      <c r="H47" s="107"/>
-      <c r="I47" s="107"/>
-      <c r="J47" s="107"/>
-      <c r="K47" s="107"/>
-      <c r="L47" s="116"/>
-    </row>
-    <row r="48" spans="1:12" ht="42.9" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="73" t="s">
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="55"/>
+    </row>
+    <row r="50" spans="1:12" ht="42.9" customHeight="1">
+      <c r="A50" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="108" t="s">
+      <c r="B50" s="49"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="E48" s="108"/>
-      <c r="F48" s="108"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="108"/>
-      <c r="I48" s="108"/>
-      <c r="J48" s="108"/>
-      <c r="K48" s="108"/>
-      <c r="L48" s="109"/>
-    </row>
-    <row r="49" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-    </row>
-    <row r="50" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="110" t="s">
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
+      <c r="H50" s="50"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="50"/>
+      <c r="K50" s="50"/>
+      <c r="L50" s="51"/>
+    </row>
+    <row r="51" spans="1:12" ht="6" customHeight="1">
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+    </row>
+    <row r="52" spans="1:12" ht="21" customHeight="1">
+      <c r="A52" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="111"/>
-      <c r="C50" s="112"/>
-      <c r="D50" s="112"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="112"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="112"/>
-      <c r="K50" s="112"/>
-      <c r="L50" s="113"/>
-    </row>
-    <row r="51" spans="1:12" ht="130.80000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="119" t="s">
+      <c r="B52" s="44"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="46"/>
+      <c r="G52" s="46"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="47"/>
+    </row>
+    <row r="53" spans="1:12" ht="130.80000000000001" customHeight="1">
+      <c r="A53" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="120"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="120"/>
-      <c r="E51" s="120"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="120"/>
-      <c r="H51" s="120"/>
-      <c r="I51" s="120"/>
-      <c r="J51" s="120"/>
-      <c r="K51" s="120"/>
-      <c r="L51" s="121"/>
-    </row>
-    <row r="52" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-    </row>
-    <row r="53" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="110" t="s">
+      <c r="B53" s="41"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="42"/>
+    </row>
+    <row r="54" spans="1:12" ht="6" customHeight="1">
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+    </row>
+    <row r="55" spans="1:12" ht="21" customHeight="1">
+      <c r="A55" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B53" s="111"/>
-      <c r="C53" s="112"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="112"/>
-      <c r="H53" s="112"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="112"/>
-      <c r="K53" s="112"/>
-      <c r="L53" s="113"/>
-    </row>
-    <row r="54" spans="1:12" ht="146.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="119" t="s">
+      <c r="B55" s="44"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="46"/>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="46"/>
+      <c r="L55" s="47"/>
+    </row>
+    <row r="56" spans="1:12" ht="146.4" customHeight="1">
+      <c r="A56" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B54" s="120"/>
-      <c r="C54" s="120"/>
-      <c r="D54" s="120"/>
-      <c r="E54" s="120"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="120"/>
-      <c r="H54" s="120"/>
-      <c r="I54" s="120"/>
-      <c r="J54" s="120"/>
-      <c r="K54" s="120"/>
-      <c r="L54" s="121"/>
-    </row>
-    <row r="55" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-    </row>
-    <row r="56" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="110" t="s">
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="41"/>
+      <c r="L56" s="42"/>
+    </row>
+    <row r="57" spans="1:12" ht="6" customHeight="1">
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+    </row>
+    <row r="58" spans="1:12" ht="21" customHeight="1">
+      <c r="A58" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B56" s="111"/>
-      <c r="C56" s="111"/>
-      <c r="D56" s="111"/>
-      <c r="E56" s="111"/>
-      <c r="F56" s="111"/>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="111"/>
-      <c r="L56" s="122"/>
-    </row>
-    <row r="57" spans="1:12" ht="25.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="119" t="s">
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="44"/>
+      <c r="L58" s="45"/>
+    </row>
+    <row r="59" spans="1:12" ht="25.8" customHeight="1">
+      <c r="A59" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="120"/>
-      <c r="C57" s="120"/>
-      <c r="D57" s="120"/>
-      <c r="E57" s="120"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="120"/>
-      <c r="H57" s="120"/>
-      <c r="I57" s="120"/>
-      <c r="J57" s="120"/>
-      <c r="K57" s="120"/>
-      <c r="L57" s="121"/>
-    </row>
-    <row r="58" spans="1:12" ht="6" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="59" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="41"/>
+      <c r="L59" s="42"/>
+    </row>
+    <row r="60" spans="1:12" ht="6" customHeight="1"/>
+    <row r="61" spans="1:12" ht="25.2" customHeight="1"/>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="A54:L54"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:L53"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="D48:L48"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:L50"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="C43:L43"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C37:L37"/>
-    <mergeCell ref="C38:L38"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C15:L15"/>
+  <mergeCells count="72">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:J5"/>
     <mergeCell ref="J10:L11"/>
     <mergeCell ref="A8:B9"/>
     <mergeCell ref="F8:L8"/>
@@ -4133,25 +4148,58 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:J2"/>
-    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C37:L37"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="C45:L45"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="C44:L44"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="C43:L43"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:L52"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A58:L58"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:L55"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
     <dataValidation imeMode="fullKatakana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7:L7 C2:J2" xr:uid="{B5425B2E-3631-48B9-B6A5-30C71F58C7A9}"/>
-    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C11 A39:B43 A14:B36" xr:uid="{E170A088-1339-427F-9097-8455E44C1D1F}"/>
+    <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C11 A14:B36 A39:B45" xr:uid="{E170A088-1339-427F-9097-8455E44C1D1F}"/>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.43307086614173229" right="0.43307086614173229" top="0.70866141732283472" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4178,19 +4226,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B26E16B-22C0-4E48-9DE1-B61E3A8E413D}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -4205,81 +4253,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42928952-FA90-4134-9EA0-2287960AEBD3}">
   <dimension ref="A1:L58"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.69921875" customWidth="1"/>
-    <col min="2" max="2" width="7.09765625" customWidth="1"/>
-    <col min="3" max="3" width="5.69921875" customWidth="1"/>
-    <col min="4" max="4" width="16.69921875" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="3.3984375" customWidth="1"/>
-    <col min="7" max="7" width="5.59765625" customWidth="1"/>
-    <col min="8" max="8" width="3.59765625" customWidth="1"/>
+    <col min="6" max="6" width="3.44140625" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" customWidth="1"/>
+    <col min="8" max="8" width="3.5546875" customWidth="1"/>
     <col min="9" max="9" width="7" customWidth="1"/>
-    <col min="10" max="10" width="8.3984375" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" customWidth="1"/>
     <col min="12" max="12" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="200" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1">
+      <c r="A1" s="131" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="200"/>
+      <c r="B1" s="131"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="201">
+      <c r="E1" s="132">
         <v>45575</v>
       </c>
-      <c r="F1" s="201"/>
-      <c r="G1" s="201"/>
-      <c r="H1" s="201"/>
-      <c r="I1" s="201"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
       <c r="J1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="202" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="203"/>
-      <c r="C2" s="204" t="s">
+      <c r="B2" s="134"/>
+      <c r="C2" s="135" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="205"/>
-    </row>
-    <row r="3" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="192" t="s">
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="136"/>
+    </row>
+    <row r="3" spans="1:12" ht="45" customHeight="1">
+      <c r="A3" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="194" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="196"/>
-    </row>
-    <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="197" t="s">
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
+      <c r="J3" s="127"/>
+    </row>
+    <row r="4" spans="1:12" ht="21" customHeight="1">
+      <c r="A4" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="198"/>
-      <c r="C4" s="199">
+      <c r="B4" s="129"/>
+      <c r="C4" s="130">
         <v>35190</v>
       </c>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
       <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
@@ -4297,535 +4345,535 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="190" t="s">
+    <row r="5" spans="1:12" ht="21" customHeight="1">
+      <c r="A5" s="153" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="191"/>
-      <c r="C5" s="186" t="s">
+      <c r="B5" s="154"/>
+      <c r="C5" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="186"/>
-      <c r="E5" s="186" t="s">
+      <c r="D5" s="147"/>
+      <c r="E5" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="186"/>
-      <c r="G5" s="186" t="s">
+      <c r="F5" s="147"/>
+      <c r="G5" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="186"/>
-      <c r="I5" s="186"/>
-      <c r="J5" s="187"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="188" t="s">
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
+      <c r="J5" s="148"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="149" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="189"/>
-      <c r="C7" s="160" t="s">
+      <c r="B7" s="150"/>
+      <c r="C7" s="151" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="160"/>
-      <c r="L7" s="161"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="176" t="s">
+      <c r="D7" s="151"/>
+      <c r="E7" s="151"/>
+      <c r="F7" s="151"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="152"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="177"/>
+      <c r="B8" s="138"/>
       <c r="C8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="180" t="s">
+      <c r="D8" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="180"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="181"/>
-      <c r="H8" s="181"/>
-      <c r="I8" s="181"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="181"/>
-      <c r="L8" s="182"/>
-    </row>
-    <row r="9" spans="1:12" ht="51.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="178"/>
-      <c r="B9" s="179"/>
-      <c r="C9" s="183" t="s">
+      <c r="E8" s="141"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="142"/>
+      <c r="L8" s="143"/>
+    </row>
+    <row r="9" spans="1:12" ht="51.6" customHeight="1">
+      <c r="A9" s="139"/>
+      <c r="B9" s="140"/>
+      <c r="C9" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
-      <c r="F9" s="184"/>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="185"/>
-    </row>
-    <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="172" t="s">
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="145"/>
+      <c r="K9" s="145"/>
+      <c r="L9" s="146"/>
+    </row>
+    <row r="10" spans="1:12" ht="21" customHeight="1">
+      <c r="A10" s="167" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="173"/>
-      <c r="C10" s="174" t="s">
+      <c r="B10" s="168"/>
+      <c r="C10" s="169" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="175"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="162" t="s">
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="170"/>
+      <c r="H10" s="155" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="163"/>
-      <c r="J10" s="164" t="s">
+      <c r="I10" s="156"/>
+      <c r="J10" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="165"/>
-      <c r="L10" s="166"/>
-    </row>
-    <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="136" t="s">
+      <c r="K10" s="158"/>
+      <c r="L10" s="159"/>
+    </row>
+    <row r="11" spans="1:12" ht="21" customHeight="1">
+      <c r="A11" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="137"/>
-      <c r="C11" s="169" t="s">
+      <c r="B11" s="163"/>
+      <c r="C11" s="164" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="169"/>
-      <c r="H11" s="170"/>
-      <c r="I11" s="171"/>
-      <c r="J11" s="167"/>
-      <c r="K11" s="167"/>
-      <c r="L11" s="168"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="D11" s="164"/>
+      <c r="E11" s="164"/>
+      <c r="F11" s="164"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
+      <c r="L11" s="161"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="158" t="s">
+      <c r="C13" s="173" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="158"/>
-      <c r="G13" s="158"/>
-      <c r="H13" s="158"/>
-      <c r="I13" s="158"/>
-      <c r="J13" s="158"/>
-      <c r="K13" s="158"/>
-      <c r="L13" s="159"/>
-    </row>
-    <row r="14" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D13" s="173"/>
+      <c r="E13" s="173"/>
+      <c r="F13" s="173"/>
+      <c r="G13" s="173"/>
+      <c r="H13" s="173"/>
+      <c r="I13" s="173"/>
+      <c r="J13" s="173"/>
+      <c r="K13" s="173"/>
+      <c r="L13" s="174"/>
+    </row>
+    <row r="14" spans="1:12" ht="21" customHeight="1">
       <c r="A14" s="15"/>
       <c r="B14" s="16"/>
-      <c r="C14" s="160" t="s">
+      <c r="C14" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="160"/>
-      <c r="E14" s="160"/>
-      <c r="F14" s="160"/>
-      <c r="G14" s="160"/>
-      <c r="H14" s="160"/>
-      <c r="I14" s="160"/>
-      <c r="J14" s="160"/>
-      <c r="K14" s="160"/>
-      <c r="L14" s="161"/>
-    </row>
-    <row r="15" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
+      <c r="H14" s="151"/>
+      <c r="I14" s="151"/>
+      <c r="J14" s="151"/>
+      <c r="K14" s="151"/>
+      <c r="L14" s="152"/>
+    </row>
+    <row r="15" spans="1:12" ht="21" customHeight="1">
       <c r="A15" s="13">
         <v>2012</v>
       </c>
       <c r="B15" s="5">
         <v>9</v>
       </c>
-      <c r="C15" s="144" t="s">
+      <c r="C15" s="171" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="145"/>
-    </row>
-    <row r="16" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D15" s="171"/>
+      <c r="E15" s="171"/>
+      <c r="F15" s="171"/>
+      <c r="G15" s="171"/>
+      <c r="H15" s="171"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="171"/>
+      <c r="K15" s="171"/>
+      <c r="L15" s="172"/>
+    </row>
+    <row r="16" spans="1:12" ht="21" customHeight="1">
       <c r="A16" s="13">
         <v>2015</v>
       </c>
       <c r="B16" s="5">
         <v>7</v>
       </c>
-      <c r="C16" s="144" t="s">
+      <c r="C16" s="171" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
-      <c r="I16" s="144"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="144"/>
-      <c r="L16" s="145"/>
-    </row>
-    <row r="17" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D16" s="171"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="171"/>
+      <c r="G16" s="171"/>
+      <c r="H16" s="171"/>
+      <c r="I16" s="171"/>
+      <c r="J16" s="171"/>
+      <c r="K16" s="171"/>
+      <c r="L16" s="172"/>
+    </row>
+    <row r="17" spans="1:12" ht="21" customHeight="1">
       <c r="A17" s="13">
         <v>2015</v>
       </c>
       <c r="B17" s="5">
         <v>9</v>
       </c>
-      <c r="C17" s="144" t="s">
+      <c r="C17" s="171" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="144"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="144"/>
-      <c r="L17" s="145"/>
-    </row>
-    <row r="18" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="171"/>
+      <c r="G17" s="171"/>
+      <c r="H17" s="171"/>
+      <c r="I17" s="171"/>
+      <c r="J17" s="171"/>
+      <c r="K17" s="171"/>
+      <c r="L17" s="172"/>
+    </row>
+    <row r="18" spans="1:12" ht="21" customHeight="1">
       <c r="A18" s="13">
         <v>2019</v>
       </c>
       <c r="B18" s="5">
         <v>7</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="C18" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="144"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="144"/>
-      <c r="I18" s="144"/>
-      <c r="J18" s="144"/>
-      <c r="K18" s="144"/>
-      <c r="L18" s="145"/>
-    </row>
-    <row r="19" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="171"/>
+      <c r="E18" s="171"/>
+      <c r="F18" s="171"/>
+      <c r="G18" s="171"/>
+      <c r="H18" s="171"/>
+      <c r="I18" s="171"/>
+      <c r="J18" s="171"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="172"/>
+    </row>
+    <row r="19" spans="1:12" ht="21" customHeight="1">
       <c r="A19" s="13">
         <v>2020</v>
       </c>
       <c r="B19" s="5">
         <v>4</v>
       </c>
-      <c r="C19" s="144" t="s">
+      <c r="C19" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="144"/>
-      <c r="I19" s="144"/>
-      <c r="J19" s="144"/>
-      <c r="K19" s="144"/>
-      <c r="L19" s="145"/>
-    </row>
-    <row r="20" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D19" s="171"/>
+      <c r="E19" s="171"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="171"/>
+      <c r="H19" s="171"/>
+      <c r="I19" s="171"/>
+      <c r="J19" s="171"/>
+      <c r="K19" s="171"/>
+      <c r="L19" s="172"/>
+    </row>
+    <row r="20" spans="1:12" ht="21" customHeight="1">
       <c r="A20" s="13">
         <v>2022</v>
       </c>
       <c r="B20" s="5">
         <v>3</v>
       </c>
-      <c r="C20" s="144" t="s">
+      <c r="C20" s="171" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="144"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="144"/>
-      <c r="I20" s="144"/>
-      <c r="J20" s="144"/>
-      <c r="K20" s="144"/>
-      <c r="L20" s="145"/>
-    </row>
-    <row r="21" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D20" s="171"/>
+      <c r="E20" s="171"/>
+      <c r="F20" s="171"/>
+      <c r="G20" s="171"/>
+      <c r="H20" s="171"/>
+      <c r="I20" s="171"/>
+      <c r="J20" s="171"/>
+      <c r="K20" s="171"/>
+      <c r="L20" s="172"/>
+    </row>
+    <row r="21" spans="1:12" ht="21" customHeight="1">
       <c r="A21" s="13">
         <v>2024</v>
       </c>
       <c r="B21" s="5">
         <v>4</v>
       </c>
-      <c r="C21" s="144" t="s">
+      <c r="C21" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="144"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
-      <c r="I21" s="144"/>
-      <c r="J21" s="144"/>
-      <c r="K21" s="144"/>
-      <c r="L21" s="145"/>
-    </row>
-    <row r="22" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D21" s="171"/>
+      <c r="E21" s="171"/>
+      <c r="F21" s="171"/>
+      <c r="G21" s="171"/>
+      <c r="H21" s="171"/>
+      <c r="I21" s="171"/>
+      <c r="J21" s="171"/>
+      <c r="K21" s="171"/>
+      <c r="L21" s="172"/>
+    </row>
+    <row r="22" spans="1:12" ht="21" customHeight="1">
       <c r="A22" s="13">
         <v>2026</v>
       </c>
       <c r="B22" s="5">
         <v>3</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="144"/>
-      <c r="I22" s="144"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="144"/>
-      <c r="L22" s="145"/>
-    </row>
-    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D22" s="171"/>
+      <c r="E22" s="171"/>
+      <c r="F22" s="171"/>
+      <c r="G22" s="171"/>
+      <c r="H22" s="171"/>
+      <c r="I22" s="171"/>
+      <c r="J22" s="171"/>
+      <c r="K22" s="171"/>
+      <c r="L22" s="172"/>
+    </row>
+    <row r="23" spans="1:12" ht="21" customHeight="1">
       <c r="A23" s="13"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
-      <c r="I23" s="144"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="144"/>
-      <c r="L23" s="145"/>
-    </row>
-    <row r="24" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
+      <c r="H23" s="171"/>
+      <c r="I23" s="171"/>
+      <c r="J23" s="171"/>
+      <c r="K23" s="171"/>
+      <c r="L23" s="172"/>
+    </row>
+    <row r="24" spans="1:12" ht="21" customHeight="1">
       <c r="A24" s="13"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="144" t="s">
+      <c r="C24" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="144"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
-      <c r="I24" s="144"/>
-      <c r="J24" s="144"/>
-      <c r="K24" s="144"/>
-      <c r="L24" s="145"/>
-    </row>
-    <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
+      <c r="H24" s="171"/>
+      <c r="I24" s="171"/>
+      <c r="J24" s="171"/>
+      <c r="K24" s="171"/>
+      <c r="L24" s="172"/>
+    </row>
+    <row r="25" spans="1:12" ht="21" customHeight="1">
       <c r="A25" s="13">
         <v>2019</v>
       </c>
       <c r="B25" s="5">
         <v>8</v>
       </c>
-      <c r="C25" s="144" t="s">
+      <c r="C25" s="171" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="144"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
-      <c r="I25" s="144"/>
-      <c r="J25" s="144"/>
-      <c r="K25" s="144"/>
-      <c r="L25" s="145"/>
-    </row>
-    <row r="26" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="171"/>
+      <c r="G25" s="171"/>
+      <c r="H25" s="171"/>
+      <c r="I25" s="171"/>
+      <c r="J25" s="171"/>
+      <c r="K25" s="171"/>
+      <c r="L25" s="172"/>
+    </row>
+    <row r="26" spans="1:12" ht="21" customHeight="1">
       <c r="A26" s="13">
         <v>2020</v>
       </c>
       <c r="B26" s="5">
         <v>3</v>
       </c>
-      <c r="C26" s="144" t="s">
+      <c r="C26" s="171" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="144"/>
-      <c r="K26" s="144"/>
-      <c r="L26" s="145"/>
-    </row>
-    <row r="27" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
+      <c r="H26" s="171"/>
+      <c r="I26" s="171"/>
+      <c r="J26" s="171"/>
+      <c r="K26" s="171"/>
+      <c r="L26" s="172"/>
+    </row>
+    <row r="27" spans="1:12" ht="21" customHeight="1">
       <c r="A27" s="13"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="154"/>
-      <c r="G27" s="154"/>
-      <c r="H27" s="154"/>
-      <c r="I27" s="154"/>
-      <c r="J27" s="154"/>
-      <c r="K27" s="154"/>
-      <c r="L27" s="155"/>
-    </row>
-    <row r="28" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C27" s="175"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="175"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="175"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="175"/>
+      <c r="L27" s="176"/>
+    </row>
+    <row r="28" spans="1:12" ht="21" customHeight="1">
       <c r="A28" s="13"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="144" t="s">
+      <c r="C28" s="171" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="144"/>
-      <c r="E28" s="144"/>
-      <c r="F28" s="144"/>
-      <c r="G28" s="144"/>
-      <c r="H28" s="144"/>
-      <c r="I28" s="144"/>
-      <c r="J28" s="144"/>
-      <c r="K28" s="144"/>
-      <c r="L28" s="145"/>
-    </row>
-    <row r="29" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="171"/>
+      <c r="G28" s="171"/>
+      <c r="H28" s="171"/>
+      <c r="I28" s="171"/>
+      <c r="J28" s="171"/>
+      <c r="K28" s="171"/>
+      <c r="L28" s="172"/>
+    </row>
+    <row r="29" spans="1:12" ht="21" customHeight="1">
       <c r="A29" s="13">
         <v>2020</v>
       </c>
       <c r="B29" s="5">
         <v>4</v>
       </c>
-      <c r="C29" s="144" t="s">
+      <c r="C29" s="171" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="144"/>
-      <c r="J29" s="144"/>
-      <c r="K29" s="144"/>
-      <c r="L29" s="145"/>
-    </row>
-    <row r="30" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D29" s="171"/>
+      <c r="E29" s="171"/>
+      <c r="F29" s="171"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+      <c r="I29" s="171"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="172"/>
+    </row>
+    <row r="30" spans="1:12" ht="21" customHeight="1">
       <c r="A30" s="13">
         <v>2021</v>
       </c>
       <c r="B30" s="5">
         <v>4</v>
       </c>
-      <c r="C30" s="144" t="s">
+      <c r="C30" s="171" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="144"/>
-      <c r="E30" s="144"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="144"/>
-      <c r="I30" s="144"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="145"/>
-    </row>
-    <row r="31" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D30" s="171"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
+      <c r="H30" s="171"/>
+      <c r="I30" s="171"/>
+      <c r="J30" s="171"/>
+      <c r="K30" s="171"/>
+      <c r="L30" s="172"/>
+    </row>
+    <row r="31" spans="1:12" ht="21" customHeight="1">
       <c r="A31" s="13">
         <v>2022</v>
       </c>
       <c r="B31" s="5">
         <v>4</v>
       </c>
-      <c r="C31" s="144" t="s">
+      <c r="C31" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="144"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="144"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="144"/>
-      <c r="I31" s="144"/>
-      <c r="J31" s="144"/>
-      <c r="K31" s="144"/>
-      <c r="L31" s="145"/>
-    </row>
-    <row r="32" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D31" s="171"/>
+      <c r="E31" s="171"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="171"/>
+      <c r="H31" s="171"/>
+      <c r="I31" s="171"/>
+      <c r="J31" s="171"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="172"/>
+    </row>
+    <row r="32" spans="1:12" ht="21" customHeight="1">
       <c r="A32" s="13"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="144" t="s">
+      <c r="C32" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="144"/>
-      <c r="E32" s="144"/>
-      <c r="F32" s="144"/>
-      <c r="G32" s="144"/>
-      <c r="H32" s="144"/>
-      <c r="I32" s="144"/>
-      <c r="J32" s="144"/>
-      <c r="K32" s="144"/>
-      <c r="L32" s="145"/>
-    </row>
-    <row r="33" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
+      <c r="H32" s="171"/>
+      <c r="I32" s="171"/>
+      <c r="J32" s="171"/>
+      <c r="K32" s="171"/>
+      <c r="L32" s="172"/>
+    </row>
+    <row r="33" spans="1:12" ht="21" customHeight="1">
       <c r="A33" s="13"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="154"/>
-      <c r="D33" s="154"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="154"/>
-      <c r="I33" s="154"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="155"/>
-    </row>
-    <row r="34" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C33" s="175"/>
+      <c r="D33" s="175"/>
+      <c r="E33" s="175"/>
+      <c r="F33" s="175"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="175"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="175"/>
+      <c r="K33" s="175"/>
+      <c r="L33" s="176"/>
+    </row>
+    <row r="34" spans="1:12" ht="21" customHeight="1">
       <c r="A34" s="13"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="154"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="154"/>
-      <c r="I34" s="154"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="154"/>
-      <c r="L34" s="155"/>
-    </row>
-    <row r="35" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C34" s="175"/>
+      <c r="D34" s="175"/>
+      <c r="E34" s="175"/>
+      <c r="F34" s="175"/>
+      <c r="G34" s="175"/>
+      <c r="H34" s="175"/>
+      <c r="I34" s="175"/>
+      <c r="J34" s="175"/>
+      <c r="K34" s="175"/>
+      <c r="L34" s="176"/>
+    </row>
+    <row r="35" spans="1:12" ht="21" customHeight="1">
       <c r="A35" s="14"/>
       <c r="B35" s="18"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="156"/>
-      <c r="G35" s="156"/>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="156"/>
-      <c r="K35" s="156"/>
-      <c r="L35" s="157"/>
-    </row>
-    <row r="36" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C35" s="177"/>
+      <c r="D35" s="177"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="177"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="177"/>
+      <c r="J35" s="177"/>
+      <c r="K35" s="177"/>
+      <c r="L35" s="178"/>
+    </row>
+    <row r="36" spans="1:12" ht="21" customHeight="1">
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -4837,297 +4885,341 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:12">
       <c r="A37" s="11" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="158" t="s">
+      <c r="C37" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="D37" s="158"/>
-      <c r="E37" s="158"/>
-      <c r="F37" s="158"/>
-      <c r="G37" s="158"/>
-      <c r="H37" s="158"/>
-      <c r="I37" s="158"/>
-      <c r="J37" s="158"/>
-      <c r="K37" s="158"/>
-      <c r="L37" s="159"/>
-    </row>
-    <row r="38" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D37" s="173"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="173"/>
+      <c r="J37" s="173"/>
+      <c r="K37" s="173"/>
+      <c r="L37" s="174"/>
+    </row>
+    <row r="38" spans="1:12" ht="21" customHeight="1">
       <c r="A38" s="12">
         <v>2023</v>
       </c>
       <c r="B38" s="9">
         <v>3</v>
       </c>
-      <c r="C38" s="152" t="s">
+      <c r="C38" s="185" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="152"/>
-      <c r="H38" s="152"/>
-      <c r="I38" s="152"/>
-      <c r="J38" s="152"/>
-      <c r="K38" s="152"/>
-      <c r="L38" s="153"/>
-    </row>
-    <row r="39" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="185"/>
+      <c r="E38" s="185"/>
+      <c r="F38" s="185"/>
+      <c r="G38" s="185"/>
+      <c r="H38" s="185"/>
+      <c r="I38" s="185"/>
+      <c r="J38" s="185"/>
+      <c r="K38" s="185"/>
+      <c r="L38" s="186"/>
+    </row>
+    <row r="39" spans="1:12" ht="21" customHeight="1">
       <c r="A39" s="13">
         <v>2024</v>
       </c>
       <c r="B39" s="5">
         <v>3</v>
       </c>
-      <c r="C39" s="144" t="s">
+      <c r="C39" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="144"/>
-      <c r="E39" s="144"/>
-      <c r="F39" s="144"/>
-      <c r="G39" s="144"/>
-      <c r="H39" s="144"/>
-      <c r="I39" s="144"/>
-      <c r="J39" s="144"/>
-      <c r="K39" s="144"/>
-      <c r="L39" s="145"/>
-    </row>
-    <row r="40" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="171"/>
+      <c r="E39" s="171"/>
+      <c r="F39" s="171"/>
+      <c r="G39" s="171"/>
+      <c r="H39" s="171"/>
+      <c r="I39" s="171"/>
+      <c r="J39" s="171"/>
+      <c r="K39" s="171"/>
+      <c r="L39" s="172"/>
+    </row>
+    <row r="40" spans="1:12" ht="21" customHeight="1">
       <c r="A40" s="13">
         <v>2024</v>
       </c>
       <c r="B40" s="5">
         <v>3</v>
       </c>
-      <c r="C40" s="142" t="s">
+      <c r="C40" s="187" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="144"/>
-      <c r="E40" s="144"/>
-      <c r="F40" s="144"/>
-      <c r="G40" s="144"/>
-      <c r="H40" s="144"/>
-      <c r="I40" s="144"/>
-      <c r="J40" s="144"/>
-      <c r="K40" s="144"/>
-      <c r="L40" s="145"/>
-    </row>
-    <row r="41" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D40" s="171"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="171"/>
+      <c r="G40" s="171"/>
+      <c r="H40" s="171"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="171"/>
+      <c r="K40" s="171"/>
+      <c r="L40" s="172"/>
+    </row>
+    <row r="41" spans="1:12" ht="21" customHeight="1">
       <c r="A41" s="13">
         <v>2024</v>
       </c>
       <c r="B41" s="5">
         <v>6</v>
       </c>
-      <c r="C41" s="144" t="s">
+      <c r="C41" s="171" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="144"/>
-      <c r="E41" s="144"/>
-      <c r="F41" s="144"/>
-      <c r="G41" s="144"/>
-      <c r="H41" s="144"/>
-      <c r="I41" s="144"/>
-      <c r="J41" s="144"/>
-      <c r="K41" s="144"/>
-      <c r="L41" s="145"/>
-    </row>
-    <row r="42" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D41" s="171"/>
+      <c r="E41" s="171"/>
+      <c r="F41" s="171"/>
+      <c r="G41" s="171"/>
+      <c r="H41" s="171"/>
+      <c r="I41" s="171"/>
+      <c r="J41" s="171"/>
+      <c r="K41" s="171"/>
+      <c r="L41" s="172"/>
+    </row>
+    <row r="42" spans="1:12" ht="21" customHeight="1">
       <c r="A42" s="14"/>
       <c r="B42" s="18"/>
-      <c r="C42" s="146"/>
-      <c r="D42" s="146"/>
-      <c r="E42" s="146"/>
-      <c r="F42" s="146"/>
-      <c r="G42" s="146"/>
-      <c r="H42" s="146"/>
-      <c r="I42" s="146"/>
-      <c r="J42" s="146"/>
-      <c r="K42" s="146"/>
-      <c r="L42" s="147"/>
-    </row>
-    <row r="44" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="148" t="s">
+      <c r="C42" s="179"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="179"/>
+      <c r="F42" s="179"/>
+      <c r="G42" s="179"/>
+      <c r="H42" s="179"/>
+      <c r="I42" s="179"/>
+      <c r="J42" s="179"/>
+      <c r="K42" s="179"/>
+      <c r="L42" s="180"/>
+    </row>
+    <row r="44" spans="1:12" ht="37.950000000000003" customHeight="1">
+      <c r="A44" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="149"/>
-      <c r="C44" s="149"/>
-      <c r="D44" s="150" t="s">
+      <c r="B44" s="182"/>
+      <c r="C44" s="182"/>
+      <c r="D44" s="183" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="150"/>
-      <c r="F44" s="150"/>
-      <c r="G44" s="150"/>
-      <c r="H44" s="150"/>
-      <c r="I44" s="150"/>
-      <c r="J44" s="150"/>
-      <c r="K44" s="150"/>
-      <c r="L44" s="151"/>
-    </row>
-    <row r="45" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="140" t="s">
+      <c r="E44" s="183"/>
+      <c r="F44" s="183"/>
+      <c r="G44" s="183"/>
+      <c r="H44" s="183"/>
+      <c r="I44" s="183"/>
+      <c r="J44" s="183"/>
+      <c r="K44" s="183"/>
+      <c r="L44" s="184"/>
+    </row>
+    <row r="45" spans="1:12" ht="37.950000000000003" customHeight="1">
+      <c r="A45" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="141"/>
-      <c r="C45" s="141"/>
-      <c r="D45" s="142" t="s">
+      <c r="B45" s="195"/>
+      <c r="C45" s="195"/>
+      <c r="D45" s="187" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="142"/>
-      <c r="F45" s="142"/>
-      <c r="G45" s="142"/>
-      <c r="H45" s="142"/>
-      <c r="I45" s="142"/>
-      <c r="J45" s="142"/>
-      <c r="K45" s="142"/>
-      <c r="L45" s="143"/>
-    </row>
-    <row r="46" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="140" t="s">
+      <c r="E45" s="187"/>
+      <c r="F45" s="187"/>
+      <c r="G45" s="187"/>
+      <c r="H45" s="187"/>
+      <c r="I45" s="187"/>
+      <c r="J45" s="187"/>
+      <c r="K45" s="187"/>
+      <c r="L45" s="196"/>
+    </row>
+    <row r="46" spans="1:12" ht="37.950000000000003" customHeight="1">
+      <c r="A46" s="194" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="141"/>
-      <c r="C46" s="141"/>
-      <c r="D46" s="142" t="s">
+      <c r="B46" s="195"/>
+      <c r="C46" s="195"/>
+      <c r="D46" s="187" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="142"/>
-      <c r="F46" s="142"/>
-      <c r="G46" s="142"/>
-      <c r="H46" s="142"/>
-      <c r="I46" s="142"/>
-      <c r="J46" s="142"/>
-      <c r="K46" s="142"/>
-      <c r="L46" s="143"/>
-    </row>
-    <row r="47" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="136" t="s">
+      <c r="E46" s="187"/>
+      <c r="F46" s="187"/>
+      <c r="G46" s="187"/>
+      <c r="H46" s="187"/>
+      <c r="I46" s="187"/>
+      <c r="J46" s="187"/>
+      <c r="K46" s="187"/>
+      <c r="L46" s="196"/>
+    </row>
+    <row r="47" spans="1:12" ht="37.950000000000003" customHeight="1">
+      <c r="A47" s="162" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="137"/>
-      <c r="C47" s="137"/>
-      <c r="D47" s="138" t="s">
+      <c r="B47" s="163"/>
+      <c r="C47" s="163"/>
+      <c r="D47" s="188" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="139"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A49" s="132" t="s">
+      <c r="E47" s="188"/>
+      <c r="F47" s="188"/>
+      <c r="G47" s="188"/>
+      <c r="H47" s="188"/>
+      <c r="I47" s="188"/>
+      <c r="J47" s="188"/>
+      <c r="K47" s="188"/>
+      <c r="L47" s="189"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="190" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="133"/>
-      <c r="C49" s="134"/>
-      <c r="D49" s="134"/>
-      <c r="E49" s="134"/>
-      <c r="F49" s="134"/>
-      <c r="G49" s="134"/>
-      <c r="H49" s="134"/>
-      <c r="I49" s="134"/>
-      <c r="J49" s="134"/>
-      <c r="K49" s="134"/>
-      <c r="L49" s="135"/>
-    </row>
-    <row r="50" spans="1:12" ht="150" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="126" t="s">
+      <c r="B49" s="191"/>
+      <c r="C49" s="192"/>
+      <c r="D49" s="192"/>
+      <c r="E49" s="192"/>
+      <c r="F49" s="192"/>
+      <c r="G49" s="192"/>
+      <c r="H49" s="192"/>
+      <c r="I49" s="192"/>
+      <c r="J49" s="192"/>
+      <c r="K49" s="192"/>
+      <c r="L49" s="193"/>
+    </row>
+    <row r="50" spans="1:12" ht="150" customHeight="1">
+      <c r="A50" s="200" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="127"/>
-      <c r="C50" s="127"/>
-      <c r="D50" s="127"/>
-      <c r="E50" s="127"/>
-      <c r="F50" s="127"/>
-      <c r="G50" s="127"/>
-      <c r="H50" s="127"/>
-      <c r="I50" s="127"/>
-      <c r="J50" s="127"/>
-      <c r="K50" s="127"/>
-      <c r="L50" s="128"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A52" s="132" t="s">
+      <c r="B50" s="201"/>
+      <c r="C50" s="201"/>
+      <c r="D50" s="201"/>
+      <c r="E50" s="201"/>
+      <c r="F50" s="201"/>
+      <c r="G50" s="201"/>
+      <c r="H50" s="201"/>
+      <c r="I50" s="201"/>
+      <c r="J50" s="201"/>
+      <c r="K50" s="201"/>
+      <c r="L50" s="202"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="190" t="s">
         <v>16</v>
       </c>
-      <c r="B52" s="133"/>
-      <c r="C52" s="134"/>
-      <c r="D52" s="134"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="134"/>
-      <c r="G52" s="134"/>
-      <c r="H52" s="134"/>
-      <c r="I52" s="134"/>
-      <c r="J52" s="134"/>
-      <c r="K52" s="134"/>
-      <c r="L52" s="135"/>
-    </row>
-    <row r="53" spans="1:12" ht="150" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="126" t="s">
+      <c r="B52" s="191"/>
+      <c r="C52" s="192"/>
+      <c r="D52" s="192"/>
+      <c r="E52" s="192"/>
+      <c r="F52" s="192"/>
+      <c r="G52" s="192"/>
+      <c r="H52" s="192"/>
+      <c r="I52" s="192"/>
+      <c r="J52" s="192"/>
+      <c r="K52" s="192"/>
+      <c r="L52" s="193"/>
+    </row>
+    <row r="53" spans="1:12" ht="150" customHeight="1">
+      <c r="A53" s="200" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="127"/>
-      <c r="C53" s="127"/>
-      <c r="D53" s="127"/>
-      <c r="E53" s="127"/>
-      <c r="F53" s="127"/>
-      <c r="G53" s="127"/>
-      <c r="H53" s="127"/>
-      <c r="I53" s="127"/>
-      <c r="J53" s="127"/>
-      <c r="K53" s="127"/>
-      <c r="L53" s="128"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A55" s="129" t="s">
+      <c r="B53" s="201"/>
+      <c r="C53" s="201"/>
+      <c r="D53" s="201"/>
+      <c r="E53" s="201"/>
+      <c r="F53" s="201"/>
+      <c r="G53" s="201"/>
+      <c r="H53" s="201"/>
+      <c r="I53" s="201"/>
+      <c r="J53" s="201"/>
+      <c r="K53" s="201"/>
+      <c r="L53" s="202"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="130"/>
-      <c r="C55" s="130"/>
-      <c r="D55" s="130"/>
-      <c r="E55" s="130"/>
-      <c r="F55" s="130"/>
-      <c r="G55" s="130"/>
-      <c r="H55" s="130"/>
-      <c r="I55" s="130"/>
-      <c r="J55" s="130"/>
-      <c r="K55" s="130"/>
-      <c r="L55" s="131"/>
-    </row>
-    <row r="56" spans="1:12" ht="79.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="123"/>
-      <c r="B56" s="124"/>
-      <c r="C56" s="124"/>
-      <c r="D56" s="124"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="124"/>
-      <c r="G56" s="124"/>
-      <c r="H56" s="124"/>
-      <c r="I56" s="124"/>
-      <c r="J56" s="124"/>
-      <c r="K56" s="124"/>
-      <c r="L56" s="125"/>
-    </row>
-    <row r="58" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.45"/>
+      <c r="B55" s="204"/>
+      <c r="C55" s="204"/>
+      <c r="D55" s="204"/>
+      <c r="E55" s="204"/>
+      <c r="F55" s="204"/>
+      <c r="G55" s="204"/>
+      <c r="H55" s="204"/>
+      <c r="I55" s="204"/>
+      <c r="J55" s="204"/>
+      <c r="K55" s="204"/>
+      <c r="L55" s="205"/>
+    </row>
+    <row r="56" spans="1:12" ht="79.95" customHeight="1">
+      <c r="A56" s="197"/>
+      <c r="B56" s="198"/>
+      <c r="C56" s="198"/>
+      <c r="D56" s="198"/>
+      <c r="E56" s="198"/>
+      <c r="F56" s="198"/>
+      <c r="G56" s="198"/>
+      <c r="H56" s="198"/>
+      <c r="I56" s="198"/>
+      <c r="J56" s="198"/>
+      <c r="K56" s="198"/>
+      <c r="L56" s="199"/>
+    </row>
+    <row r="58" spans="1:12" ht="25.2" customHeight="1"/>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E1:I1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:J2"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A53:L53"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:L52"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:L49"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:L46"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="C42:L42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="C40:L40"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="C37:L37"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="C20:L20"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="C16:L16"/>
+    <mergeCell ref="C17:L17"/>
+    <mergeCell ref="C18:L18"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:L11"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="A8:B9"/>
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:L8"/>
@@ -5138,58 +5230,14 @@
     <mergeCell ref="C7:L7"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:L11"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C16:L16"/>
-    <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="C20:L20"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="C37:L37"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C32:L32"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C41:L41"/>
-    <mergeCell ref="C42:L42"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="C38:L38"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="C40:L40"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:L49"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="A56:L56"/>
-    <mergeCell ref="A53:L53"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:L52"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:J2"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
